--- a/refs/heads/master/StructureDefinition-PatientLE.xlsx
+++ b/refs/heads/master/StructureDefinition-PatientLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:17:51+00:00</t>
+    <t>2023-02-15T16:22:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-PatientLE.xlsx
+++ b/refs/heads/master/StructureDefinition-PatientLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:22:21+00:00</t>
+    <t>2023-02-15T20:04:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-PatientLE.xlsx
+++ b/refs/heads/master/StructureDefinition-PatientLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T20:04:03+00:00</t>
+    <t>2023-02-16T23:28:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-PatientLE.xlsx
+++ b/refs/heads/master/StructureDefinition-PatientLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-16T23:28:10+00:00</t>
+    <t>2023-02-17T19:45:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-PatientLE.xlsx
+++ b/refs/heads/master/StructureDefinition-PatientLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-17T19:45:07+00:00</t>
+    <t>2023-02-20T03:17:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-PatientLE.xlsx
+++ b/refs/heads/master/StructureDefinition-PatientLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T03:17:07+00:00</t>
+    <t>2023-02-20T03:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-PatientLE.xlsx
+++ b/refs/heads/master/StructureDefinition-PatientLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T03:26:30+00:00</t>
+    <t>2023-02-20T22:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-PatientLE.xlsx
+++ b/refs/heads/master/StructureDefinition-PatientLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T22:25:44+00:00</t>
+    <t>2023-02-21T14:23:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-PatientLE.xlsx
+++ b/refs/heads/master/StructureDefinition-PatientLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-21T14:23:26+00:00</t>
+    <t>2023-02-21T19:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-PatientLE.xlsx
+++ b/refs/heads/master/StructureDefinition-PatientLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-21T19:28:17+00:00</t>
+    <t>2023-02-22T15:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-PatientLE.xlsx
+++ b/refs/heads/master/StructureDefinition-PatientLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T15:40:59+00:00</t>
+    <t>2023-02-22T16:44:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-PatientLE.xlsx
+++ b/refs/heads/master/StructureDefinition-PatientLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T16:44:04+00:00</t>
+    <t>2023-02-22T20:35:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-PatientLE.xlsx
+++ b/refs/heads/master/StructureDefinition-PatientLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T20:35:25+00:00</t>
+    <t>2023-02-27T14:20:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-PatientLE.xlsx
+++ b/refs/heads/master/StructureDefinition-PatientLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-27T14:20:24+00:00</t>
+    <t>2023-02-27T15:22:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-PatientLE.xlsx
+++ b/refs/heads/master/StructureDefinition-PatientLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-27T15:22:20+00:00</t>
+    <t>2023-03-02T15:13:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-PatientLE.xlsx
+++ b/refs/heads/master/StructureDefinition-PatientLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T15:13:04+00:00</t>
+    <t>2023-03-02T20:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-PatientLE.xlsx
+++ b/refs/heads/master/StructureDefinition-PatientLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T20:01:22+00:00</t>
+    <t>2023-03-03T15:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-PatientLE.xlsx
+++ b/refs/heads/master/StructureDefinition-PatientLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-03T15:04:24+00:00</t>
+    <t>2023-03-06T14:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-PatientLE.xlsx
+++ b/refs/heads/master/StructureDefinition-PatientLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-06T14:18:09+00:00</t>
+    <t>2023-03-08T00:16:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-PatientLE.xlsx
+++ b/refs/heads/master/StructureDefinition-PatientLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-08T00:16:35+00:00</t>
+    <t>2023-03-08T00:32:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-PatientLE.xlsx
+++ b/refs/heads/master/StructureDefinition-PatientLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-08T00:32:01+00:00</t>
+    <t>2023-03-09T19:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -7585,11 +7585,9 @@
       <c r="W44" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="X44" t="s" s="2">
-        <v>203</v>
-      </c>
+      <c r="X44" s="2"/>
       <c r="Y44" t="s" s="2">
-        <v>204</v>
+        <v>303</v>
       </c>
       <c r="Z44" t="s" s="2">
         <v>78</v>
@@ -8607,11 +8605,13 @@
         <v>78</v>
       </c>
       <c r="W53" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="X53" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Y53" t="s" s="2">
-        <v>303</v>
+        <v>78</v>
       </c>
       <c r="Z53" t="s" s="2">
         <v>78</v>
@@ -9476,7 +9476,7 @@
         <v>76</v>
       </c>
       <c r="F61" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>85</v>
@@ -10097,11 +10097,9 @@
       <c r="W66" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="X66" t="s" s="2">
-        <v>203</v>
-      </c>
+      <c r="X66" s="2"/>
       <c r="Y66" t="s" s="2">
-        <v>204</v>
+        <v>303</v>
       </c>
       <c r="Z66" t="s" s="2">
         <v>78</v>
@@ -11119,11 +11117,13 @@
         <v>78</v>
       </c>
       <c r="W75" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="X75" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Y75" t="s" s="2">
-        <v>303</v>
+        <v>78</v>
       </c>
       <c r="Z75" t="s" s="2">
         <v>78</v>

--- a/refs/heads/master/StructureDefinition-PatientLE.xlsx
+++ b/refs/heads/master/StructureDefinition-PatientLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:11:45+00:00</t>
+    <t>2023-03-09T19:22:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-PatientLE.xlsx
+++ b/refs/heads/master/StructureDefinition-PatientLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:22:45+00:00</t>
+    <t>2023-03-09T19:42:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-PatientLE.xlsx
+++ b/refs/heads/master/StructureDefinition-PatientLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:42:39+00:00</t>
+    <t>2023-03-10T17:11:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-PatientLE.xlsx
+++ b/refs/heads/master/StructureDefinition-PatientLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-10T17:11:36+00:00</t>
+    <t>2023-03-10T20:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-PatientLE.xlsx
+++ b/refs/heads/master/StructureDefinition-PatientLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-10T20:13:24+00:00</t>
+    <t>2023-03-11T11:08:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
